--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/sep-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/sep-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/sep-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/sep-2025.xlsx
@@ -623,7 +623,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1521,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2098,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2289,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2354,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2602,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2667,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2732,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2797,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2862,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2992,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3122,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3187,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3252,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3317,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3382,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3447,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3512,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3577,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3764,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3890,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4142,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4207,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4272,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4337,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4402,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4467,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4593,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4658,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4723,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4910,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4975,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5101,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5166,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5231,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5296,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5361,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5487,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5613,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5678,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5743,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5808,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5873,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5938,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6003,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6068,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6133,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6198,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6263,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6328,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6515,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6641,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6706,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6771,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6836,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6962,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7027,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7275,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7340,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7405,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7470,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7535,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7661,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7726,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7791,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8043,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8169,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8234,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8299,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8364,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8490,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8555,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8620,11 @@
           <t>77.883.662-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8685,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8750,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8876,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9002,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9128,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9315,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9380,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9445,11 @@
           <t>78.091.613-3</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9510,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9575,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9640,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9705,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9770,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9896,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10083,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10148,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10213,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10278,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10343,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10408,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10473,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10599,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10664,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10729,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10916,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10981,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11107,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11172,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11298,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11363,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11489,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11554,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11619,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11684,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11810,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11875,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11940,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12005,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12131,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12196,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12261,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12326,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12391,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12456,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12582,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12647,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12712,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12777,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12842,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12907,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12972,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13037,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13102,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13167,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13232,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13297,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13427,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13492,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13557,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13683,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13748,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13874,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13939,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14004,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14069,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14134,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14199,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14264,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14329,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14394,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14459,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14585,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14650,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14715,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14902,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14967,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15032,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15097,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15162,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15227,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15292,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15357,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15727,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15792,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15857,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15922,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16048,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16174,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16300,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16365,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16430,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16495,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16560,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16625,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16690,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16755,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16820,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16885,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17011,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17076,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17141,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17267,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17332,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17397,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17523,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17588,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17718,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17783,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17848,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17913,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18039,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18104,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18169,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18234,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18299,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18364,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18490,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18555,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18864,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18990,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19116,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19181,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19246,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19433,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19559,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19624,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19750,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19876,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19941,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20006,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20071,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20197,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20262,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20327,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20392,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20457,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20522,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20652,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20778,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20843,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20908,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20973,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21038,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21103,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21290,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21355,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21420,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21485,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21550,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21615,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21680,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21745,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21810,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21875,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22184,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22249,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22314,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22379,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22505,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22570,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22635,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22700,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22765,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22830,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22895,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22960,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23025,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23090,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23155,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23220,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23285,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23411,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23476,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23541,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23606,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23671,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23736,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23801,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23866,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23931,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24122,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24187,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24252,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24378,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24687,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24752,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24817,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24943,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25008,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25138,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25203,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25268,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25394,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25459,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25585,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25650,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25715,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25780,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25845,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25910,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26036,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26101,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26227,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26292,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26357,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26487,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26552,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26617,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26743,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26869,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26934,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +26999,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27064,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27259,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27324,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27389,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27454,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27645,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27710,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27775,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27840,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27905,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27970,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28035,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28100,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28165,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28230,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28295,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28360,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28425,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28490,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28555,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28620,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28685,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28750,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28815,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28880,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +28945,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29010,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29075,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29140,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29205,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29270,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29396,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29461,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29526,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29591,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29717,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29782,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29847,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29912,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29977,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +30042,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30107,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30172,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30237,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30363,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30428,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30493,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30558,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30623,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30871,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30936,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +31001,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31066,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31131,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31196,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31322,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31387,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31452,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31517,11 @@
           <t>77.883.083-3</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31582,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31647,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31834,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +32021,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32086,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32338,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32464,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +32590,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32842,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32907,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32972,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33159,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33224,11 @@
           <t>77.883.083-3</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33289,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
